--- a/outputs/daily/hr_rankings_2026-10-15.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-15.xlsx
@@ -1608,11 +1608,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>675660</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>58.7</v>
+        <v>57.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1633,7 +1645,7 @@
         <v>79.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -1642,7 +1654,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
         <v>8.800000000000001</v>
@@ -1684,7 +1696,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1721,7 +1733,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1794,12 +1806,36 @@
           <t>0.2679</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -1815,56 +1851,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1878,61 +1914,65 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>53.3</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="R6" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>34.9</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1949,142 +1989,134 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2095,44 +2127,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>54.2</v>
+        <v>55.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2146,65 +2190,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>34.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2221,110 +2261,142 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -3451,24 +3523,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -3481,26 +3553,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3514,26 +3586,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>63.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3547,7 +3619,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3572,7 +3644,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3589,12 +3661,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3604,12 +3676,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3619,97 +3691,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
@@ -3727,12 +3799,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3757,7 +3829,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3776,7 +3848,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3790,11 +3862,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
         <v>35.6</v>
@@ -3803,13 +3875,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3823,7 +3895,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3870,22 +3942,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3895,67 +3967,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4003,24 +4075,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -4033,12 +4105,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>48.6</v>
       </c>
@@ -4054,26 +4138,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>55.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>65.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4087,7 +4171,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4112,7 +4196,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4129,105 +4213,129 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.2892</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4781</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -4243,44 +4351,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4294,65 +4414,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.3</v>
+        <v>23.4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4374,22 +4490,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4399,80 +4515,112 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4483,47 +4631,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4532,7 +4680,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4546,58 +4694,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>25.8</v>
+        <v>47.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>38.7</v>
+        <v>35.6</v>
       </c>
       <c r="R16" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>13.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4617,12 +4769,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4632,127 +4784,119 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4763,24 +4907,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -4793,26 +4937,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4826,26 +4970,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>47.1</v>
+        <v>55.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>13.3</v>
+        <v>18</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4859,7 +5003,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4884,7 +5028,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4901,12 +5045,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4916,112 +5060,112 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -5319,12 +5463,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5349,14 +5493,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>675660</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>46.4</v>
+        <v>45.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5370,26 +5526,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5403,7 +5559,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5428,7 +5584,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5445,27 +5601,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5475,75 +5631,99 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5559,24 +5739,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -5589,26 +5769,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5626,22 +5806,22 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q20" t="n">
         <v>39.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>35.6</v>
       </c>
       <c r="R20" t="n">
         <v>27.6</v>
       </c>
       <c r="S20" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -5655,7 +5835,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -5680,7 +5860,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -5702,22 +5882,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5727,97 +5907,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -5835,24 +6015,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -5865,14 +6045,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>44.1</v>
+        <v>44.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -5890,22 +6082,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="R21" t="n">
         <v>27.6</v>
       </c>
       <c r="S21" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -5919,7 +6111,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -5944,7 +6136,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -5961,12 +6153,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -5976,12 +6168,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -5991,75 +6183,99 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1823</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
@@ -6075,24 +6291,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -6105,26 +6321,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.8</v>
+        <v>44.3</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6142,22 +6358,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>38.2</v>
+        <v>36.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R22" t="n">
         <v>27.6</v>
       </c>
       <c r="S22" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T22" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>25.3</v>
+        <v>66</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6171,7 +6387,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6196,7 +6412,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6213,27 +6429,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6243,97 +6459,97 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr"/>
@@ -6351,32 +6567,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6386,12 +6602,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -6400,7 +6616,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6414,61 +6630,65 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>20.9</v>
+        <v>38.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>40.1</v>
+        <v>35.6</v>
       </c>
       <c r="R23" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S23" t="n">
-        <v>76.2</v>
+        <v>71.7</v>
       </c>
       <c r="T23" t="n">
         <v>80</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6485,27 +6705,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6515,112 +6735,104 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6631,44 +6843,56 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L24" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6682,65 +6906,61 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R24" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S24" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T24" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -6757,27 +6977,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -6787,80 +7007,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1925</t>
-        </is>
-      </c>
-      <c r="BA24" t="inlineStr"/>
-      <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
-      <c r="BF24" t="inlineStr"/>
-      <c r="BG24" t="inlineStr"/>
-      <c r="BH24" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -8551,12 +8803,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Enrique Hernandez</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -8581,14 +8833,26 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>675660</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L31" t="n">
-        <v>37.9</v>
+        <v>38.5</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8602,26 +8866,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>33.9</v>
+        <v>32.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="R31" t="n">
         <v>27.6</v>
       </c>
       <c r="S31" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T31" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U31" t="n">
-        <v>12</v>
+        <v>28.5</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8635,7 +8899,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8660,7 +8924,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8677,27 +8941,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8707,75 +8971,99 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>14.87</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1658</t>
-        </is>
-      </c>
-      <c r="BA31" t="inlineStr"/>
-      <c r="BB31" t="inlineStr"/>
-      <c r="BC31" t="inlineStr"/>
-      <c r="BD31" t="inlineStr"/>
-      <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
+          <t>0.1735</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BE31" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BF31" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
@@ -9071,44 +9359,56 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>571771</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Enrique Hernandez</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>37.3</v>
+        <v>36.9</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9122,65 +9422,61 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>32.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R33" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S33" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>28.5</v>
+        <v>38.3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9202,22 +9498,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9227,80 +9523,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>39.49</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>89.39</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>99.9102</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3751</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2814</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>14.87</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1735</t>
-        </is>
-      </c>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
-      <c r="BF33" t="inlineStr"/>
-      <c r="BG33" t="inlineStr"/>
-      <c r="BH33" t="inlineStr"/>
+          <t>0.0707</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9311,32 +9639,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9346,21 +9674,21 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9374,61 +9702,65 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>7.1</v>
+        <v>33.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="R34" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S34" t="n">
-        <v>52.4</v>
+        <v>47.9</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>38.3</v>
+        <v>12</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9445,12 +9777,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9460,12 +9792,12 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9475,112 +9807,104 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>70.22</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -11618,11 +11942,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>675660</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>58.7</v>
+        <v>57.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -11643,7 +11979,7 @@
         <v>79.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
@@ -11652,7 +11988,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U5" t="n">
         <v>8.800000000000001</v>
@@ -11694,7 +12030,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -11731,7 +12067,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -11804,12 +12140,36 @@
           <t>0.2679</t>
         </is>
       </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -11825,56 +12185,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.2</v>
+        <v>55.4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -11888,61 +12248,65 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>53.3</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="R6" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>94.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>34.9</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -11959,142 +12323,134 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1874</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.7</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12105,44 +12461,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>54.2</v>
+        <v>55.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12156,65 +12524,61 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>53.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>40.1</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>34.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -12231,110 +12595,142 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>0.1874</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -13461,24 +13857,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Teoscar Hernandez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -13491,26 +13887,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -13524,26 +13920,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>63.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -13557,7 +13953,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -13582,7 +13978,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -13599,12 +13995,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -13614,12 +14010,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -13629,97 +14025,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr"/>
@@ -13737,12 +14133,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -13767,7 +14163,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -13786,7 +14182,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -13800,11 +14196,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>36.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q13" t="n">
         <v>35.6</v>
@@ -13813,13 +14209,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -13833,7 +14229,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -13880,22 +14276,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -13905,67 +14301,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -14013,24 +14409,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>571970</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -14043,12 +14439,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>48.6</v>
       </c>
@@ -14064,26 +14472,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>55.1</v>
+        <v>36.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>95.5</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>65.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14097,7 +14505,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -14122,7 +14530,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -14139,105 +14547,129 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.2892</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4781</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>14.13</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>51.36</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2347</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -14253,44 +14685,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-16T00:00:00Z</t>
+          <t>2026-10-15T17:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Griffin Jax</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>643377</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14304,65 +14748,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>56.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.3</v>
+        <v>23.4</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -14384,22 +14824,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -14409,80 +14849,112 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1727</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>0.1591</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>8.77</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.3923</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1478</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>22.6</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Out To CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -14493,47 +14965,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-15T17:00:00Z</t>
+          <t>2026-10-16T00:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14542,7 +15014,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -14556,58 +15028,62 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>25.8</v>
+        <v>47.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>38.7</v>
+        <v>35.6</v>
       </c>
       <c r="R16" t="n">
-        <v>56.6</v>
+        <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>13.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14627,12 +15103,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -14642,127 +15118,119 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>77.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3923</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1478</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>Out To CF</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -14773,24 +15241,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -14803,26 +15271,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -14836,26 +15304,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>47.1</v>
+        <v>55.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>39.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>13.3</v>
+        <v>18</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -14869,7 +15337,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -14894,7 +15362,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -14911,12 +15379,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -14926,112 +15394,112 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>77.44</t>
+          <t>14.13</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr"/>
@@ -15329,12 +15797,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15359,14 +15827,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shane Drohan</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>675660</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>46.4</v>
+        <v>45.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15380,26 +15860,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.2</v>
+        <v>39.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T19" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -15413,7 +15893,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -15438,7 +15918,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -15455,27 +15935,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -15485,75 +15965,99 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+          <t>0.1823</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.7</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -15569,24 +16073,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -15599,26 +16103,26 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -15636,22 +16140,22 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Q20" t="n">
         <v>39.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>35.6</v>
       </c>
       <c r="R20" t="n">
         <v>27.6</v>
       </c>
       <c r="S20" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>37.8</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -15665,7 +16169,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -15690,7 +16194,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -15712,22 +16216,22 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -15737,97 +16241,97 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr"/>
@@ -15845,24 +16349,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>2026-10-16T00:00:00Z</t>
@@ -15875,14 +16379,26 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>44.1</v>
+        <v>44.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -15900,22 +16416,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>32.7</v>
+        <v>39.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="R21" t="n">
         <v>27.6</v>
       </c>
       <c r="S21" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>29.2</v>
+        <v>37.8</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -15929,7 +16445,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -15954,7 +16470,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr"/>
@@ -15971,12 +16487,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -15986,12 +16502,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16001,75 +16517,99 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1823</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
